--- a/demo_data/care_plans.xlsx
+++ b/demo_data/care_plans.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hypothyroidism</t>
+          <t>Schizophrenia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -501,19 +501,19 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H2" t="n">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -527,12 +527,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4 medications</t>
+          <t>2 medications</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Eye review due</t>
+          <t>Foot review due</t>
         </is>
       </c>
     </row>
@@ -549,7 +549,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Breast Cancer</t>
+          <t>Epilepsy</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -559,19 +559,19 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H3" t="n">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -585,12 +585,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>3 medications</t>
+          <t>4 medications</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>HbA1c overdue</t>
+          <t>Foot review due</t>
         </is>
       </c>
     </row>
@@ -612,24 +612,24 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H4" t="n">
-        <v>2200</v>
+        <v>1800</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2 medications</t>
+          <t>4 medications</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -665,29 +665,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hypertension</t>
+          <t>Type 2 Diabetes</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H5" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -696,17 +696,17 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>&lt;7%</t>
+          <t>&lt;8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4 medications</t>
+          <t>2 medications</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Eye review due</t>
         </is>
       </c>
     </row>
@@ -723,22 +723,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hypertension</t>
+          <t>Breast Cancer</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -749,12 +749,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>&lt;125/75</t>
+          <t>&lt;140/90</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>&lt;8%</t>
+          <t>&lt;7.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>Type 2 Diabetes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -791,19 +791,19 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-02-07</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H7" t="n">
-        <v>2000</v>
+        <v>2200</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -817,12 +817,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4 medications</t>
+          <t>2 medications</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Foot review due</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -844,24 +844,24 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Dr. Arjun Verma</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-01-09</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="H8" t="n">
-        <v>1800</v>
+        <v>2200</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>&lt;7%</t>
+          <t>&lt;7.5%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>HbA1c overdue</t>
         </is>
       </c>
     </row>
@@ -897,33 +897,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hypertension</t>
+          <t>Hypothyroidism</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>8000</v>
       </c>
       <c r="H9" t="n">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>&lt;125/75</t>
+          <t>&lt;140/90</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -933,12 +933,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3 medications</t>
+          <t>2 medications</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Eye review due</t>
+          <t>Foot review due</t>
         </is>
       </c>
     </row>
@@ -955,38 +955,38 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>COPD</t>
+          <t>CKD Stage 3</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Dr. Sunita Sharma</t>
+          <t>Dr. Suresh Reddy</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-01-24</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H10" t="n">
         <v>1600</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>&lt;130/80</t>
+          <t>&lt;140/90</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>&lt;7%</t>
+          <t>&lt;7.5%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Eye review due</t>
+          <t>Foot review due</t>
         </is>
       </c>
     </row>
@@ -1013,33 +1013,33 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Epilepsy</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="H11" t="n">
         <v>2200</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>&lt;130/80</t>
+          <t>&lt;125/75</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2 medications</t>
+          <t>4 medications</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Eye review due</t>
         </is>
       </c>
     </row>
@@ -1071,33 +1071,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Schizophrenia</t>
+          <t>Hypothyroidism</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H12" t="n">
-        <v>2200</v>
+        <v>1800</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>&lt;140/90</t>
+          <t>&lt;130/80</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4 medications</t>
+          <t>3 medications</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Foot review due</t>
+          <t>HbA1c overdue</t>
         </is>
       </c>
     </row>
@@ -1129,38 +1129,38 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Epilepsy</t>
+          <t>Hypothyroidism</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Dr. Vikram Rao</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H13" t="n">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>&lt;130/80</t>
+          <t>&lt;140/90</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>&lt;7%</t>
+          <t>&lt;7.5%</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>HbA1c overdue</t>
         </is>
       </c>
     </row>
@@ -1187,48 +1187,48 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Epilepsy</t>
+          <t>Schizophrenia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Arjun Verma</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="H14" t="n">
-        <v>2200</v>
+        <v>1600</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>&lt;125/75</t>
+          <t>&lt;140/90</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>&lt;7%</t>
+          <t>&lt;8%</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>3 medications</t>
+          <t>4 medications</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Foot review due</t>
+          <t>Eye review due</t>
         </is>
       </c>
     </row>
@@ -1245,29 +1245,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CKD Stage 3</t>
+          <t>Hypertension</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Dr. Priya Mehta</t>
+          <t>Dr. Sunita Sharma</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>8000</v>
       </c>
       <c r="H15" t="n">
-        <v>2000</v>
+        <v>1800</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Eye review due</t>
+          <t>HbA1c overdue</t>
         </is>
       </c>
     </row>
@@ -1303,33 +1303,33 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Type 2 Diabetes</t>
+          <t>COPD</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Dr. Suresh Reddy</t>
+          <t>Dr. Kavita Nair</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>6000</v>
       </c>
       <c r="H16" t="n">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>&lt;125/75</t>
+          <t>&lt;130/80</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4 medications</t>
+          <t>2 medications</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1361,43 +1361,43 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CKD Stage 3</t>
+          <t>Hypothyroidism</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Dr. Deepa Iyer</t>
+          <t>Dr. Rajesh Kumar</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H17" t="n">
-        <v>2200</v>
+        <v>1800</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>&lt;140/90</t>
+          <t>&lt;130/80</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>&lt;8%</t>
+          <t>&lt;7%</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4 medications</t>
+          <t>2 medications</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CAD</t>
+          <t>Epilepsy</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1429,38 +1429,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="H18" t="n">
-        <v>1800</v>
+        <v>1600</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>&lt;140/90</t>
+          <t>&lt;130/80</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>&lt;7%</t>
+          <t>&lt;7.5%</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2 medications</t>
+          <t>4 medications</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Foot review due</t>
+          <t>HbA1c overdue</t>
         </is>
       </c>
     </row>
@@ -1477,17 +1477,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hypothyroidism</t>
+          <t>CAD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Dr. Sunita Sharma</t>
+          <t>Dr. Deepa Iyer</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1496,14 +1496,14 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="H19" t="n">
         <v>2000</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>&lt;125/75</t>
+          <t>&lt;130/80</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>HbA1c overdue</t>
+          <t>Foot review due</t>
         </is>
       </c>
     </row>
@@ -1535,33 +1535,33 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hypertension</t>
+          <t>CKD Stage 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Dr. Rajesh Kumar</t>
+          <t>Dr. Suresh Reddy</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H20" t="n">
-        <v>2200</v>
+        <v>1800</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>&lt;125/75</t>
+          <t>&lt;130/80</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Eye review due</t>
         </is>
       </c>
     </row>
@@ -1593,29 +1593,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Type 2 Diabetes</t>
+          <t>COPD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Dr. Kavita Nair</t>
+          <t>Dr. Anita Singh</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>6000</v>
       </c>
       <c r="H21" t="n">
-        <v>1600</v>
+        <v>2200</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1624,17 +1624,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>&lt;7%</t>
+          <t>&lt;7.5%</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4 medications</t>
+          <t>3 medications</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Foot review due</t>
+          <t>None</t>
         </is>
       </c>
     </row>
